--- a/output/Data and Chart Outputs/morocco_capacity_annual.xlsx
+++ b/output/Data and Chart Outputs/morocco_capacity_annual.xlsx
@@ -1028,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,10 +1091,10 @@
         <v>2016</v>
       </c>
       <c r="C2" t="n">
-        <v>1770.039</v>
+        <v>1770</v>
       </c>
       <c r="D2" t="n">
-        <v>2895</v>
+        <v>2456.4</v>
       </c>
       <c r="E2" t="n">
         <v>892</v>
@@ -1106,13 +1106,13 @@
         <v>1230</v>
       </c>
       <c r="H2" t="n">
-        <v>1019</v>
+        <v>898.4</v>
       </c>
       <c r="I2" t="n">
         <v>181</v>
       </c>
       <c r="J2" t="n">
-        <v>8821.039000000001</v>
+        <v>8261.799999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1123,10 +1123,10 @@
         <v>2017</v>
       </c>
       <c r="C3" t="n">
-        <v>1770</v>
+        <v>1770.039</v>
       </c>
       <c r="D3" t="n">
-        <v>4281</v>
+        <v>2895</v>
       </c>
       <c r="E3" t="n">
         <v>892</v>
@@ -1138,53 +1138,53 @@
         <v>1230</v>
       </c>
       <c r="H3" t="n">
-        <v>1221</v>
+        <v>1019</v>
       </c>
       <c r="I3" t="n">
-        <v>711</v>
+        <v>181</v>
       </c>
       <c r="J3" t="n">
-        <v>10939</v>
+        <v>8821.039000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>44197</v>
+        <v>43101</v>
       </c>
       <c r="B4" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C4" t="n">
         <v>1770</v>
       </c>
       <c r="D4" t="n">
-        <v>4116</v>
+        <v>4281</v>
       </c>
       <c r="E4" t="n">
-        <v>841.1</v>
+        <v>892</v>
       </c>
       <c r="F4" t="n">
         <v>834</v>
       </c>
       <c r="G4" t="n">
-        <v>1110</v>
+        <v>1230</v>
       </c>
       <c r="H4" t="n">
-        <v>1466</v>
+        <v>1221</v>
       </c>
       <c r="I4" t="n">
-        <v>830.8</v>
+        <v>711</v>
       </c>
       <c r="J4" t="n">
-        <v>10967.9</v>
+        <v>10939</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>44562</v>
+        <v>43466</v>
       </c>
       <c r="B5" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C5" t="n">
         <v>1770</v>
@@ -1193,7 +1193,7 @@
         <v>4116</v>
       </c>
       <c r="E5" t="n">
-        <v>841.1</v>
+        <v>616.1</v>
       </c>
       <c r="F5" t="n">
         <v>834</v>
@@ -1202,21 +1202,21 @@
         <v>1110</v>
       </c>
       <c r="H5" t="n">
-        <v>1553.2</v>
+        <v>1430.3</v>
       </c>
       <c r="I5" t="n">
-        <v>830.8</v>
+        <v>750.8</v>
       </c>
       <c r="J5" t="n">
-        <v>11055.1</v>
+        <v>10627.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>44927</v>
+        <v>43831</v>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C6" t="n">
         <v>1770</v>
@@ -1231,47 +1231,143 @@
         <v>834</v>
       </c>
       <c r="G6" t="n">
-        <v>1011</v>
+        <v>1110</v>
       </c>
       <c r="H6" t="n">
-        <v>2070.8</v>
+        <v>1466</v>
       </c>
       <c r="I6" t="n">
         <v>830.8</v>
       </c>
       <c r="J6" t="n">
-        <v>11473.7</v>
+        <v>10967.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>45292</v>
+        <v>44197</v>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C7" t="n">
-        <v>2120</v>
+        <v>1770</v>
       </c>
       <c r="D7" t="n">
         <v>4116</v>
       </c>
       <c r="E7" t="n">
-        <v>617.3000000000001</v>
+        <v>841.1</v>
       </c>
       <c r="F7" t="n">
         <v>834</v>
       </c>
       <c r="G7" t="n">
+        <v>1110</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1466</v>
+      </c>
+      <c r="I7" t="n">
+        <v>830.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10967.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1770</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4116</v>
+      </c>
+      <c r="E8" t="n">
+        <v>841.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>834</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1110</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1553.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>830.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11055.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1770</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4116</v>
+      </c>
+      <c r="E9" t="n">
+        <v>841.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>834</v>
+      </c>
+      <c r="G9" t="n">
         <v>1011</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H9" t="n">
+        <v>2070.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>830.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11473.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2120</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4116</v>
+      </c>
+      <c r="E10" t="n">
+        <v>617.3000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>834</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1011</v>
+      </c>
+      <c r="H10" t="n">
         <v>2390.4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I10" t="n">
         <v>928.0999999999999</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J10" t="n">
         <v>12016.8</v>
       </c>
     </row>
@@ -1286,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,7 +1452,7 @@
         <v>42370</v>
       </c>
       <c r="B2" t="n">
-        <v>2895</v>
+        <v>2456.4</v>
       </c>
       <c r="C2" t="n">
         <v>834</v>
@@ -1374,16 +1470,16 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>1770.039</v>
+        <v>1770</v>
       </c>
       <c r="I2" t="n">
         <v>181</v>
       </c>
       <c r="J2" t="n">
-        <v>8821.039000000001</v>
+        <v>8261.799999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>1019</v>
+        <v>898.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1394,7 +1490,7 @@
         <v>42736</v>
       </c>
       <c r="B3" t="n">
-        <v>4281</v>
+        <v>2895</v>
       </c>
       <c r="C3" t="n">
         <v>834</v>
@@ -1412,16 +1508,16 @@
         <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>1770</v>
+        <v>1770.039</v>
       </c>
       <c r="I3" t="n">
-        <v>711</v>
+        <v>181</v>
       </c>
       <c r="J3" t="n">
-        <v>10939</v>
+        <v>8821.039000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>1221</v>
+        <v>1019</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1429,37 +1525,37 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>44197</v>
+        <v>43101</v>
       </c>
       <c r="B4" t="n">
-        <v>4116</v>
+        <v>4281</v>
       </c>
       <c r="C4" t="n">
         <v>834</v>
       </c>
       <c r="D4" t="n">
-        <v>285.7</v>
+        <v>264</v>
       </c>
       <c r="E4" t="n">
-        <v>525</v>
+        <v>600</v>
       </c>
       <c r="F4" t="n">
-        <v>1110</v>
+        <v>1230</v>
       </c>
       <c r="G4" t="n">
-        <v>30.4</v>
+        <v>28</v>
       </c>
       <c r="H4" t="n">
         <v>1770</v>
       </c>
       <c r="I4" t="n">
-        <v>830.8</v>
+        <v>711</v>
       </c>
       <c r="J4" t="n">
-        <v>10967.9</v>
+        <v>10939</v>
       </c>
       <c r="K4" t="n">
-        <v>1466</v>
+        <v>1221</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1467,7 +1563,7 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>44562</v>
+        <v>43466</v>
       </c>
       <c r="B5" t="n">
         <v>4116</v>
@@ -1479,7 +1575,7 @@
         <v>285.7</v>
       </c>
       <c r="E5" t="n">
-        <v>525</v>
+        <v>300</v>
       </c>
       <c r="F5" t="n">
         <v>1110</v>
@@ -1491,13 +1587,13 @@
         <v>1770</v>
       </c>
       <c r="I5" t="n">
-        <v>830.8</v>
+        <v>750.8</v>
       </c>
       <c r="J5" t="n">
-        <v>11055.1</v>
+        <v>10627.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1553.2</v>
+        <v>1430.3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1505,7 +1601,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>44927</v>
+        <v>43831</v>
       </c>
       <c r="B6" t="n">
         <v>4116</v>
@@ -1520,7 +1616,7 @@
         <v>525</v>
       </c>
       <c r="F6" t="n">
-        <v>1011</v>
+        <v>1110</v>
       </c>
       <c r="G6" t="n">
         <v>30.4</v>
@@ -1532,10 +1628,10 @@
         <v>830.8</v>
       </c>
       <c r="J6" t="n">
-        <v>11473.7</v>
+        <v>10967.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2070.8</v>
+        <v>1466</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1543,7 +1639,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>45292</v>
+        <v>44197</v>
       </c>
       <c r="B7" t="n">
         <v>4116</v>
@@ -1555,27 +1651,141 @@
         <v>285.7</v>
       </c>
       <c r="E7" t="n">
+        <v>525</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1110</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I7" t="n">
+        <v>830.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10967.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1466</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4116</v>
+      </c>
+      <c r="C8" t="n">
+        <v>834</v>
+      </c>
+      <c r="D8" t="n">
+        <v>285.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>525</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1110</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I8" t="n">
+        <v>830.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11055.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1553.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4116</v>
+      </c>
+      <c r="C9" t="n">
+        <v>834</v>
+      </c>
+      <c r="D9" t="n">
+        <v>285.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>525</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1011</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I9" t="n">
+        <v>830.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11473.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2070.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4116</v>
+      </c>
+      <c r="C10" t="n">
+        <v>834</v>
+      </c>
+      <c r="D10" t="n">
+        <v>285.7</v>
+      </c>
+      <c r="E10" t="n">
         <v>300</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F10" t="n">
         <v>1011</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G10" t="n">
         <v>31.6</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H10" t="n">
         <v>2120</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I10" t="n">
         <v>928.0999999999999</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J10" t="n">
         <v>12016.8</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K10" t="n">
         <v>2390.4</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1620,7 +1830,7 @@
         <v>2019</v>
       </c>
       <c r="B2" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1636,7 +1846,7 @@
         <v>2019</v>
       </c>
       <c r="B3" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1652,7 +1862,7 @@
         <v>2019</v>
       </c>
       <c r="B4" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1668,7 +1878,7 @@
         <v>2019</v>
       </c>
       <c r="B5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1684,7 +1894,7 @@
         <v>2019</v>
       </c>
       <c r="B6" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1700,7 +1910,7 @@
         <v>2019</v>
       </c>
       <c r="B7" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1716,7 +1926,7 @@
         <v>2019</v>
       </c>
       <c r="B8" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1732,7 +1942,7 @@
         <v>2019</v>
       </c>
       <c r="B9" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1748,7 +1958,7 @@
         <v>2019</v>
       </c>
       <c r="B10" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1764,7 +1974,7 @@
         <v>2019</v>
       </c>
       <c r="B11" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,7 +1990,7 @@
         <v>2019</v>
       </c>
       <c r="B12" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,7 +2006,7 @@
         <v>2019</v>
       </c>
       <c r="B13" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1812,7 +2022,7 @@
         <v>2019</v>
       </c>
       <c r="B14" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1828,7 +2038,7 @@
         <v>2019</v>
       </c>
       <c r="B15" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1844,7 +2054,7 @@
         <v>2019</v>
       </c>
       <c r="B16" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1860,7 +2070,7 @@
         <v>2019</v>
       </c>
       <c r="B17" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1876,7 +2086,7 @@
         <v>2019</v>
       </c>
       <c r="B18" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1892,7 +2102,7 @@
         <v>2019</v>
       </c>
       <c r="B19" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1908,7 +2118,7 @@
         <v>2019</v>
       </c>
       <c r="B20" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1924,7 +2134,7 @@
         <v>2019</v>
       </c>
       <c r="B21" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1937,10 +2147,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B22" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1948,15 +2158,15 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11473.7</v>
+        <v>8261.799999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B23" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1969,10 +2179,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B24" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1980,15 +2190,15 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4116</v>
+        <v>2456.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B25" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1996,15 +2206,15 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>525</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B26" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2012,15 +2222,15 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1011</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B27" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2028,15 +2238,15 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>285.7</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B28" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2049,10 +2259,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B29" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2060,15 +2270,15 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30.4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B30" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2076,15 +2286,15 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2070.8</v>
+        <v>898.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B31" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2092,15 +2302,15 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>830.8</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B32" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2108,15 +2318,15 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11055.6</v>
+        <v>10967.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B33" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2129,10 +2339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B34" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2145,10 +2355,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B35" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2161,10 +2371,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B36" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2177,10 +2387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B37" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2193,10 +2403,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B38" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2209,10 +2419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B39" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2225,10 +2435,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B40" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2236,15 +2446,15 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1553.7</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B41" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2257,10 +2467,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B42" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2268,15 +2478,15 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10967.9</v>
+        <v>10627.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B43" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2289,10 +2499,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B44" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2305,10 +2515,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B45" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2316,15 +2526,15 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>525</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B46" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2337,10 +2547,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B47" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2353,10 +2563,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B48" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2369,10 +2579,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B49" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2385,10 +2595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B50" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2396,15 +2606,15 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1466</v>
+        <v>1430.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B51" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2412,15 +2622,15 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>830.8</v>
+        <v>750.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B52" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2428,15 +2638,15 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12016.8</v>
+        <v>11055.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B53" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2444,15 +2654,15 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2120</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B54" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2465,10 +2675,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B55" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2476,15 +2686,15 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>300</v>
+        <v>525</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B56" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2492,15 +2702,15 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1011</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B57" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2513,10 +2723,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B58" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2529,10 +2739,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B59" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2540,15 +2750,15 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B60" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2556,15 +2766,15 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2390.4</v>
+        <v>1553.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B61" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2572,15 +2782,15 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>928.0999999999999</v>
+        <v>830.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B62" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2588,15 +2798,15 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11473.7</v>
+        <v>10967.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B63" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2609,10 +2819,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B64" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2625,10 +2835,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B65" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2641,10 +2851,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B66" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2652,15 +2862,15 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1011</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B67" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2673,10 +2883,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B68" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2689,10 +2899,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B69" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2705,10 +2915,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B70" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2716,15 +2926,15 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2070.8</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B71" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2737,10 +2947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B72" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2748,15 +2958,15 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11055.1</v>
+        <v>11473.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B73" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2769,10 +2979,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B74" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2785,10 +2995,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B75" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2801,10 +3011,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B76" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2812,15 +3022,15 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1110</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B77" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2833,10 +3043,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B78" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -2849,10 +3059,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B79" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2865,10 +3075,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B80" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2876,22 +3086,822 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1553.2</v>
+        <v>2070.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B81" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11055.6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B83" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B85" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B86" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B89" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B90" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1553.7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B91" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10967.9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B93" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B94" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B95" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B96" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B97" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B98" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B99" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B100" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B101" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
         <v>2025</v>
       </c>
-      <c r="B81" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C81" t="inlineStr">
+      <c r="B102" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12016.8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B103" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B104" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B105" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B106" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B107" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B108" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B109" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B110" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>2390.4</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B111" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D111" t="n">
+        <v>928.0999999999999</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B112" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11473.7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B113" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B114" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B115" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B116" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B117" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B118" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B119" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B120" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2070.8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B121" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B122" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11055.1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B123" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B124" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B125" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B126" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B127" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B128" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B129" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B130" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1553.2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B131" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
         <v>830.8</v>
       </c>
     </row>
@@ -2939,7 +3949,7 @@
         <v>2019</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -2987,7 +3997,7 @@
         <v>2022</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -3003,7 +4013,7 @@
         <v>2023</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">

--- a/output/Data and Chart Outputs/morocco_capacity_annual.xlsx
+++ b/output/Data and Chart Outputs/morocco_capacity_annual.xlsx
@@ -1161,7 +1161,7 @@
         <v>4281</v>
       </c>
       <c r="E4" t="n">
-        <v>892</v>
+        <v>891.7</v>
       </c>
       <c r="F4" t="n">
         <v>834</v>
@@ -1170,13 +1170,13 @@
         <v>1230</v>
       </c>
       <c r="H4" t="n">
-        <v>1221</v>
+        <v>1220.3</v>
       </c>
       <c r="I4" t="n">
-        <v>711</v>
+        <v>710.8</v>
       </c>
       <c r="J4" t="n">
-        <v>10939</v>
+        <v>10937.8</v>
       </c>
     </row>
     <row r="5">
@@ -1193,7 +1193,7 @@
         <v>4116</v>
       </c>
       <c r="E5" t="n">
-        <v>616.1</v>
+        <v>916.1</v>
       </c>
       <c r="F5" t="n">
         <v>834</v>
@@ -1202,13 +1202,13 @@
         <v>1110</v>
       </c>
       <c r="H5" t="n">
-        <v>1430.3</v>
+        <v>1220.3</v>
       </c>
       <c r="I5" t="n">
-        <v>750.8</v>
+        <v>710.8</v>
       </c>
       <c r="J5" t="n">
-        <v>10627.2</v>
+        <v>10677.2</v>
       </c>
     </row>
     <row r="6">
@@ -1225,7 +1225,7 @@
         <v>4116</v>
       </c>
       <c r="E6" t="n">
-        <v>841.1</v>
+        <v>616.1</v>
       </c>
       <c r="F6" t="n">
         <v>834</v>
@@ -1234,13 +1234,13 @@
         <v>1110</v>
       </c>
       <c r="H6" t="n">
-        <v>1466</v>
+        <v>1430.3</v>
       </c>
       <c r="I6" t="n">
-        <v>830.8</v>
+        <v>750.8</v>
       </c>
       <c r="J6" t="n">
-        <v>10967.9</v>
+        <v>10627.2</v>
       </c>
     </row>
     <row r="7">
@@ -1534,7 +1534,7 @@
         <v>834</v>
       </c>
       <c r="D4" t="n">
-        <v>264</v>
+        <v>263.7</v>
       </c>
       <c r="E4" t="n">
         <v>600</v>
@@ -1549,13 +1549,13 @@
         <v>1770</v>
       </c>
       <c r="I4" t="n">
-        <v>711</v>
+        <v>710.8</v>
       </c>
       <c r="J4" t="n">
-        <v>10939</v>
+        <v>10937.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1221</v>
+        <v>1220.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
         <v>285.7</v>
       </c>
       <c r="E5" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F5" t="n">
         <v>1110</v>
@@ -1587,13 +1587,13 @@
         <v>1770</v>
       </c>
       <c r="I5" t="n">
-        <v>750.8</v>
+        <v>710.8</v>
       </c>
       <c r="J5" t="n">
-        <v>10627.2</v>
+        <v>10677.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1430.3</v>
+        <v>1220.3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         <v>285.7</v>
       </c>
       <c r="E6" t="n">
-        <v>525</v>
+        <v>300</v>
       </c>
       <c r="F6" t="n">
         <v>1110</v>
@@ -1625,13 +1625,13 @@
         <v>1770</v>
       </c>
       <c r="I6" t="n">
-        <v>830.8</v>
+        <v>750.8</v>
       </c>
       <c r="J6" t="n">
-        <v>10967.9</v>
+        <v>10627.2</v>
       </c>
       <c r="K6" t="n">
-        <v>1466</v>
+        <v>1430.3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B32" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2318,15 +2318,15 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10967.9</v>
+        <v>10677</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B33" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B34" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B35" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2366,15 +2366,15 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>525</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B36" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B37" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2398,15 +2398,15 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>285.7</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B38" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B39" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2430,15 +2430,15 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B40" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2446,15 +2446,15 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1466</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B41" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2462,15 +2462,15 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>830.8</v>
+        <v>711</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B42" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2478,15 +2478,15 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10627.2</v>
+        <v>10939</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B43" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2499,10 +2499,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B44" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2510,15 +2510,15 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4116</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B45" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2526,15 +2526,15 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B46" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2542,15 +2542,15 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1110</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B47" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2558,15 +2558,15 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>285.7</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B48" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B49" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2590,15 +2590,15 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>30.4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B50" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2606,15 +2606,15 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1430.3</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B51" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2622,15 +2622,15 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>750.8</v>
+        <v>711</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B52" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2638,15 +2638,15 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11055.6</v>
+        <v>8821.039000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B53" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2654,15 +2654,15 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1770</v>
+        <v>1770.039</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B54" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2670,15 +2670,15 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4116</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B55" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2686,15 +2686,15 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>525</v>
+        <v>600</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B56" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2702,15 +2702,15 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1110</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B57" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2718,15 +2718,15 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>285.7</v>
+        <v>264</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B58" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B59" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2750,15 +2750,15 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30.4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B60" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2766,15 +2766,15 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1553.7</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B61" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2782,12 +2782,12 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>830.8</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B62" t="n">
         <v>2020</v>
@@ -2798,12 +2798,12 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10967.9</v>
+        <v>10627.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B63" t="n">
         <v>2020</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B64" t="n">
         <v>2020</v>
@@ -2835,7 +2835,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B65" t="n">
         <v>2020</v>
@@ -2846,12 +2846,12 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>525</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B66" t="n">
         <v>2020</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B67" t="n">
         <v>2020</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B68" t="n">
         <v>2020</v>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B69" t="n">
         <v>2020</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B70" t="n">
         <v>2020</v>
@@ -2926,12 +2926,12 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1466</v>
+        <v>1430.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B71" t="n">
         <v>2020</v>
@@ -2942,15 +2942,15 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>830.8</v>
+        <v>750.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B72" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2958,15 +2958,15 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11473.7</v>
+        <v>10677.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B73" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B74" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B75" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3006,15 +3006,15 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>525</v>
+        <v>600</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B76" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3022,15 +3022,15 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1011</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B77" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B78" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B79" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3075,10 +3075,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B80" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3086,15 +3086,15 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2070.8</v>
+        <v>1220.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B81" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -3102,15 +3102,15 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>830.8</v>
+        <v>710.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B82" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3118,15 +3118,15 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11055.6</v>
+        <v>10937.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B83" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B84" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3150,15 +3150,15 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4116</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B85" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3166,15 +3166,15 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>525</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B86" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3182,15 +3182,15 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1110</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B87" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -3198,15 +3198,15 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>285.7</v>
+        <v>263.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B88" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B89" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3230,15 +3230,15 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>30.4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B90" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -3246,15 +3246,15 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1553.7</v>
+        <v>1220.3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B91" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -3262,12 +3262,12 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>830.8</v>
+        <v>710.8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B92" t="n">
         <v>2021</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B93" t="n">
         <v>2021</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B94" t="n">
         <v>2021</v>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B95" t="n">
         <v>2021</v>
@@ -3331,7 +3331,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B96" t="n">
         <v>2021</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B97" t="n">
         <v>2021</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B98" t="n">
         <v>2021</v>
@@ -3379,7 +3379,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B99" t="n">
         <v>2021</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B100" t="n">
         <v>2021</v>
@@ -3411,7 +3411,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B101" t="n">
         <v>2021</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B102" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -3438,15 +3438,15 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12016.8</v>
+        <v>10627.2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B103" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -3454,15 +3454,15 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2120</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B104" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B105" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B106" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -3502,15 +3502,15 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1011</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B107" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -3523,10 +3523,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B108" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B109" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -3550,15 +3550,15 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B110" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -3566,15 +3566,15 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2390.4</v>
+        <v>1430.3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B111" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -3582,15 +3582,15 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>928.0999999999999</v>
+        <v>750.8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B112" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -3598,15 +3598,15 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11473.7</v>
+        <v>10677.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B113" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B114" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B115" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -3646,15 +3646,15 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>525</v>
+        <v>600</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B116" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -3662,15 +3662,15 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1011</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B117" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B118" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B119" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B120" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -3726,15 +3726,15 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2070.8</v>
+        <v>1220.3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B121" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -3742,12 +3742,12 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>830.8</v>
+        <v>710.8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B122" t="n">
         <v>2022</v>
@@ -3758,12 +3758,12 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11055.1</v>
+        <v>11055.6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B123" t="n">
         <v>2022</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B124" t="n">
         <v>2022</v>
@@ -3795,7 +3795,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B125" t="n">
         <v>2022</v>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B126" t="n">
         <v>2022</v>
@@ -3827,7 +3827,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B127" t="n">
         <v>2022</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B128" t="n">
         <v>2022</v>
@@ -3859,7 +3859,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B129" t="n">
         <v>2022</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B130" t="n">
         <v>2022</v>
@@ -3886,22 +3886,1302 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1553.2</v>
+        <v>1553.7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B131" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B132" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10967.9</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B133" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B134" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B135" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B136" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B137" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B138" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B140" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B141" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B142" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10627.2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B143" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B144" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B145" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B146" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B147" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B148" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B150" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1430.3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B151" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>750.8</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11473.7</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B159" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B160" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2070.8</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B161" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B162" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11055.6</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B163" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B164" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B165" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B166" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B167" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B168" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B169" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1553.7</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B171" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B172" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10967.9</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B173" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B174" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B175" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B176" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B177" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B178" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B179" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B180" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B181" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
         <v>2025</v>
       </c>
-      <c r="B131" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C131" t="inlineStr">
+      <c r="B182" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>12016.8</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B183" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B189" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B190" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>2390.4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B191" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C191" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="D131" t="n">
+      <c r="D191" t="n">
+        <v>928.0999999999999</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B192" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>11473.7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B193" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B194" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B196" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B197" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B198" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B199" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>2070.8</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>830.8</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B202" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Total_reported</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>11055.1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B203" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B204" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Coal_steam</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Fuel_steam</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Gas_turbines</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B207" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>285.7</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Combined_cycle</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B209" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Gasoil</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B210" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1553.2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B211" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
         <v>830.8</v>
       </c>
     </row>
@@ -3965,7 +5245,7 @@
         <v>2020</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -3981,7 +5261,7 @@
         <v>2021</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -3997,7 +5277,7 @@
         <v>2022</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -4013,7 +5293,7 @@
         <v>2023</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">

--- a/output/Data and Chart Outputs/morocco_capacity_annual.xlsx
+++ b/output/Data and Chart Outputs/morocco_capacity_annual.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -814,7 +815,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -930,7 +930,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -959,7 +959,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -988,7 +988,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
